--- a/outputs/senai_relatorio_qualidade.xlsx
+++ b/outputs/senai_relatorio_qualidade.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-15 16:44:00</t>
+          <t>2026-09-29 15:58:10</t>
         </is>
       </c>
     </row>
